--- a/空课程表示例.xlsx
+++ b/空课程表示例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyy\Desktop\BuaaScheduleRender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D393C265-BCD6-4936-BE75-1F398AC2C22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5999692-2343-43DF-BE7B-ABA438E36365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6390" yWindow="4710" windowWidth="28800" windowHeight="13995" xr2:uid="{B338D730-19B2-4CB0-8696-A3C075375807}"/>
+    <workbookView xWindow="6045" yWindow="4365" windowWidth="28800" windowHeight="13995" xr2:uid="{B338D730-19B2-4CB0-8696-A3C075375807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>星期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,9 +152,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1 xx课程: a老师，b老师，c老师；
-2 xx课程：d老师；
-（备注：课程直接使用课程名，无需另外添加“课程”后缀，老师名同理）</t>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 xx课程-J3-304: a老师，b老师，c老师；
+2 xx课程-实验楼3-201：d老师；
+（备注：课程直接使用课程名，无需另外添加“课程”后缀，老师名同理。课程表中课程表格必须同高同宽，不允许换行，无法显示的部分略去，同一节课，连上的，只用在最早的时间显示全名，下面的连上使用星号*代替）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +191,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -217,19 +221,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -461,7 +452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -469,9 +460,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -486,14 +474,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -501,40 +486,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -543,8 +528,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -887,58 +875,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7">
+      <c r="C1" s="5">
         <v>1</v>
       </c>
-      <c r="D1" s="7">
+      <c r="D1" s="5">
         <v>2</v>
       </c>
-      <c r="E1" s="7">
+      <c r="E1" s="5">
         <v>3</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="5">
         <v>4</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="5">
         <v>5</v>
       </c>
-      <c r="H1" s="7">
+      <c r="H1" s="5">
         <v>6</v>
       </c>
-      <c r="I1" s="7">
+      <c r="I1" s="5">
         <v>7</v>
       </c>
-      <c r="J1" s="7">
+      <c r="J1" s="5">
         <v>8</v>
       </c>
-      <c r="K1" s="7">
+      <c r="K1" s="5">
         <v>9</v>
       </c>
-      <c r="L1" s="7">
+      <c r="L1" s="5">
         <v>10</v>
       </c>
-      <c r="M1" s="7">
+      <c r="M1" s="5">
         <v>11</v>
       </c>
-      <c r="N1" s="7">
+      <c r="N1" s="5">
         <v>12</v>
       </c>
-      <c r="O1" s="8">
+      <c r="O1" s="6">
         <v>13</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="17"/>
+      <c r="Q1" s="18"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="9"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -956,16 +944,16 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="18" t="s">
+      <c r="O2" s="7"/>
+      <c r="P2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2">
@@ -985,20 +973,22 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="18">
+      <c r="O3" s="7"/>
+      <c r="P3" s="8">
         <v>1</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1010,16 +1000,16 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="18">
+      <c r="O4" s="7"/>
+      <c r="P4" s="8">
         <v>2</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -1035,17 +1025,17 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="18">
+      <c r="O5" s="7"/>
+      <c r="P5" s="8">
         <v>3</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4">
+      <c r="A6" s="25"/>
+      <c r="B6" s="2">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
@@ -1060,16 +1050,16 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="18">
+      <c r="O6" s="7"/>
+      <c r="P6" s="8">
         <v>4</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="Q6" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -1085,16 +1075,16 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="18">
+      <c r="O7" s="7"/>
+      <c r="P7" s="8">
         <v>5</v>
       </c>
-      <c r="Q7" s="19" t="s">
+      <c r="Q7" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -1110,16 +1100,16 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="18">
+      <c r="O8" s="7"/>
+      <c r="P8" s="8">
         <v>6</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="Q8" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -1135,16 +1125,16 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="18">
+      <c r="O9" s="7"/>
+      <c r="P9" s="8">
         <v>7</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -1160,16 +1150,16 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="18">
+      <c r="O10" s="7"/>
+      <c r="P10" s="8">
         <v>8</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="Q10" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -1185,16 +1175,16 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="18">
+      <c r="O11" s="7"/>
+      <c r="P11" s="8">
         <v>9</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="Q11" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -1210,16 +1200,16 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="18">
+      <c r="O12" s="7"/>
+      <c r="P12" s="8">
         <v>10</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="Q12" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -1235,16 +1225,16 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="18">
+      <c r="O13" s="7"/>
+      <c r="P13" s="8">
         <v>11</v>
       </c>
-      <c r="Q13" s="19" t="s">
+      <c r="Q13" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -1260,16 +1250,16 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="18">
+      <c r="O14" s="7"/>
+      <c r="P14" s="8">
         <v>12</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="Q14" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -1285,16 +1275,16 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="18">
+      <c r="O15" s="7"/>
+      <c r="P15" s="8">
         <v>13</v>
       </c>
-      <c r="Q15" s="19" t="s">
+      <c r="Q15" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -1310,16 +1300,16 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="20">
+      <c r="O16" s="7"/>
+      <c r="P16" s="9">
         <v>14</v>
       </c>
-      <c r="Q16" s="21" t="s">
+      <c r="Q16" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="2">
@@ -1337,14 +1327,14 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="23"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="20"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="2">
         <v>2</v>
       </c>
@@ -1360,12 +1350,12 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="25"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="22"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="2">
         <v>3</v>
       </c>
@@ -1381,12 +1371,12 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="25"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="22"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="2">
         <v>4</v>
       </c>
@@ -1402,12 +1392,12 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="25"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="22"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="2">
         <v>5</v>
       </c>
@@ -1423,12 +1413,12 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="25"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="22"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="2">
         <v>6</v>
       </c>
@@ -1444,12 +1434,12 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="25"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="22"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="2">
         <v>7</v>
       </c>
@@ -1465,12 +1455,12 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="25"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="2">
         <v>8</v>
       </c>
@@ -1486,12 +1476,12 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="25"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="2">
         <v>9</v>
       </c>
@@ -1507,12 +1497,12 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="25"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="22"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="2">
         <v>10</v>
       </c>
@@ -1528,12 +1518,12 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="25"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="22"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="2">
         <v>11</v>
       </c>
@@ -1549,12 +1539,12 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="25"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="22"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="2">
         <v>12</v>
       </c>
@@ -1570,12 +1560,12 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="25"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="22"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="2">
         <v>13</v>
       </c>
@@ -1591,12 +1581,12 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="25"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="22"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="2">
         <v>14</v>
       </c>
@@ -1612,12 +1602,12 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="25"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="22"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2">
@@ -1635,12 +1625,12 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="25"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="22"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="2">
         <v>2</v>
       </c>
@@ -1656,12 +1646,12 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="25"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="22"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
+      <c r="A33" s="25"/>
       <c r="B33" s="2">
         <v>3</v>
       </c>
@@ -1677,12 +1667,12 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="25"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="22"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
+      <c r="A34" s="25"/>
       <c r="B34" s="2">
         <v>4</v>
       </c>
@@ -1698,12 +1688,12 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="25"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="22"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
+      <c r="A35" s="25"/>
       <c r="B35" s="2">
         <v>5</v>
       </c>
@@ -1719,12 +1709,12 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="25"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="22"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="2">
         <v>6</v>
       </c>
@@ -1740,12 +1730,12 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="25"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="22"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="2">
         <v>7</v>
       </c>
@@ -1761,12 +1751,12 @@
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="25"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="22"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="2">
         <v>8</v>
       </c>
@@ -1782,12 +1772,12 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="25"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="22"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="2">
         <v>9</v>
       </c>
@@ -1803,12 +1793,12 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="25"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="22"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="2">
         <v>10</v>
       </c>
@@ -1824,12 +1814,12 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="25"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="21"/>
+      <c r="Q40" s="22"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="2">
         <v>11</v>
       </c>
@@ -1845,12 +1835,12 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="25"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="22"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="2">
         <v>12</v>
       </c>
@@ -1866,12 +1856,12 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="25"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="22"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
+      <c r="A43" s="25"/>
       <c r="B43" s="2">
         <v>13</v>
       </c>
@@ -1887,12 +1877,12 @@
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="25"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="22"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
+      <c r="A44" s="25"/>
       <c r="B44" s="2">
         <v>14</v>
       </c>
@@ -1908,12 +1898,12 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="25"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="22"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B45" s="2">
@@ -1931,12 +1921,12 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="25"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="22"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
+      <c r="A46" s="25"/>
       <c r="B46" s="2">
         <v>2</v>
       </c>
@@ -1952,12 +1942,12 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="25"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="22"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
+      <c r="A47" s="25"/>
       <c r="B47" s="2">
         <v>3</v>
       </c>
@@ -1973,12 +1963,12 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="25"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="21"/>
+      <c r="Q47" s="22"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
+      <c r="A48" s="25"/>
       <c r="B48" s="2">
         <v>4</v>
       </c>
@@ -1994,12 +1984,12 @@
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="25"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="21"/>
+      <c r="Q48" s="22"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="2">
         <v>5</v>
       </c>
@@ -2015,12 +2005,12 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="25"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="22"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
+      <c r="A50" s="25"/>
       <c r="B50" s="2">
         <v>6</v>
       </c>
@@ -2036,12 +2026,12 @@
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="25"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="22"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
+      <c r="A51" s="25"/>
       <c r="B51" s="2">
         <v>7</v>
       </c>
@@ -2057,12 +2047,12 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="25"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="22"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
+      <c r="A52" s="25"/>
       <c r="B52" s="2">
         <v>8</v>
       </c>
@@ -2078,12 +2068,12 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="25"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="21"/>
+      <c r="Q52" s="22"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="2">
         <v>9</v>
       </c>
@@ -2099,12 +2089,12 @@
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="25"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="21"/>
+      <c r="Q53" s="22"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
+      <c r="A54" s="25"/>
       <c r="B54" s="2">
         <v>10</v>
       </c>
@@ -2120,12 +2110,12 @@
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="25"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="22"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
+      <c r="A55" s="25"/>
       <c r="B55" s="2">
         <v>11</v>
       </c>
@@ -2141,12 +2131,12 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="25"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="22"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
+      <c r="A56" s="25"/>
       <c r="B56" s="2">
         <v>12</v>
       </c>
@@ -2162,12 +2152,12 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="25"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="21"/>
+      <c r="Q56" s="22"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="2">
         <v>13</v>
       </c>
@@ -2183,12 +2173,12 @@
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="25"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="22"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="2">
         <v>14</v>
       </c>
@@ -2204,12 +2194,12 @@
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="24"/>
-      <c r="Q58" s="25"/>
+      <c r="O58" s="7"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="22"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B59" s="2">
@@ -2227,12 +2217,12 @@
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="25"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="22"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="2">
         <v>2</v>
       </c>
@@ -2248,12 +2238,12 @@
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="24"/>
-      <c r="Q60" s="25"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="22"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="2">
         <v>3</v>
       </c>
@@ -2269,12 +2259,12 @@
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="25"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="22"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="2">
         <v>4</v>
       </c>
@@ -2290,12 +2280,12 @@
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="24"/>
-      <c r="Q62" s="25"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="21"/>
+      <c r="Q62" s="22"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="2">
         <v>5</v>
       </c>
@@ -2311,12 +2301,12 @@
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="24"/>
-      <c r="Q63" s="25"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="22"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="2">
         <v>6</v>
       </c>
@@ -2332,12 +2322,12 @@
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="24"/>
-      <c r="Q64" s="25"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="22"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
+      <c r="A65" s="25"/>
       <c r="B65" s="2">
         <v>7</v>
       </c>
@@ -2353,12 +2343,12 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="24"/>
-      <c r="Q65" s="25"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="21"/>
+      <c r="Q65" s="22"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A66" s="11"/>
+      <c r="A66" s="25"/>
       <c r="B66" s="2">
         <v>8</v>
       </c>
@@ -2374,12 +2364,12 @@
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="24"/>
-      <c r="Q66" s="25"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="21"/>
+      <c r="Q66" s="22"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A67" s="11"/>
+      <c r="A67" s="25"/>
       <c r="B67" s="2">
         <v>9</v>
       </c>
@@ -2395,12 +2385,12 @@
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="24"/>
-      <c r="Q67" s="25"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="22"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
+      <c r="A68" s="25"/>
       <c r="B68" s="2">
         <v>10</v>
       </c>
@@ -2416,12 +2406,12 @@
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="25"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="22"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
+      <c r="A69" s="25"/>
       <c r="B69" s="2">
         <v>11</v>
       </c>
@@ -2437,12 +2427,12 @@
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="24"/>
-      <c r="Q69" s="25"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="22"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
+      <c r="A70" s="25"/>
       <c r="B70" s="2">
         <v>12</v>
       </c>
@@ -2458,12 +2448,12 @@
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="24"/>
-      <c r="Q70" s="25"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="22"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="2">
         <v>13</v>
       </c>
@@ -2479,12 +2469,12 @@
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
-      <c r="O71" s="10"/>
-      <c r="P71" s="24"/>
-      <c r="Q71" s="25"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="22"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
+      <c r="A72" s="25"/>
       <c r="B72" s="2">
         <v>14</v>
       </c>
@@ -2500,12 +2490,12 @@
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="24"/>
-      <c r="Q72" s="25"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="21"/>
+      <c r="Q72" s="22"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B73" s="2">
@@ -2523,12 +2513,12 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="24"/>
-      <c r="Q73" s="25"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="21"/>
+      <c r="Q73" s="22"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
+      <c r="A74" s="25"/>
       <c r="B74" s="2">
         <v>2</v>
       </c>
@@ -2544,12 +2534,12 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="24"/>
-      <c r="Q74" s="25"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="21"/>
+      <c r="Q74" s="22"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
+      <c r="A75" s="25"/>
       <c r="B75" s="2">
         <v>3</v>
       </c>
@@ -2565,12 +2555,12 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="10"/>
-      <c r="P75" s="24"/>
-      <c r="Q75" s="25"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="21"/>
+      <c r="Q75" s="22"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
+      <c r="A76" s="25"/>
       <c r="B76" s="2">
         <v>4</v>
       </c>
@@ -2586,12 +2576,12 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="10"/>
-      <c r="P76" s="24"/>
-      <c r="Q76" s="25"/>
+      <c r="O76" s="7"/>
+      <c r="P76" s="21"/>
+      <c r="Q76" s="22"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="2">
         <v>5</v>
       </c>
@@ -2607,12 +2597,12 @@
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
-      <c r="O77" s="10"/>
-      <c r="P77" s="24"/>
-      <c r="Q77" s="25"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="21"/>
+      <c r="Q77" s="22"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="2">
         <v>6</v>
       </c>
@@ -2628,12 +2618,12 @@
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
-      <c r="O78" s="10"/>
-      <c r="P78" s="24"/>
-      <c r="Q78" s="25"/>
+      <c r="O78" s="7"/>
+      <c r="P78" s="21"/>
+      <c r="Q78" s="22"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79" s="11"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="2">
         <v>7</v>
       </c>
@@ -2649,12 +2639,12 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="24"/>
-      <c r="Q79" s="25"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="21"/>
+      <c r="Q79" s="22"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A80" s="11"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="2">
         <v>8</v>
       </c>
@@ -2670,12 +2660,12 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
-      <c r="O80" s="10"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="25"/>
+      <c r="O80" s="7"/>
+      <c r="P80" s="21"/>
+      <c r="Q80" s="22"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A81" s="11"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="2">
         <v>9</v>
       </c>
@@ -2691,12 +2681,12 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
-      <c r="O81" s="10"/>
-      <c r="P81" s="24"/>
-      <c r="Q81" s="25"/>
+      <c r="O81" s="7"/>
+      <c r="P81" s="21"/>
+      <c r="Q81" s="22"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="2">
         <v>10</v>
       </c>
@@ -2712,12 +2702,12 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
-      <c r="O82" s="10"/>
-      <c r="P82" s="24"/>
-      <c r="Q82" s="25"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="21"/>
+      <c r="Q82" s="22"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83" s="11"/>
+      <c r="A83" s="25"/>
       <c r="B83" s="2">
         <v>11</v>
       </c>
@@ -2733,12 +2723,12 @@
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
-      <c r="O83" s="10"/>
-      <c r="P83" s="24"/>
-      <c r="Q83" s="25"/>
+      <c r="O83" s="7"/>
+      <c r="P83" s="21"/>
+      <c r="Q83" s="22"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A84" s="11"/>
+      <c r="A84" s="25"/>
       <c r="B84" s="2">
         <v>12</v>
       </c>
@@ -2754,12 +2744,12 @@
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
-      <c r="O84" s="10"/>
-      <c r="P84" s="24"/>
-      <c r="Q84" s="25"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="21"/>
+      <c r="Q84" s="22"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85" s="11"/>
+      <c r="A85" s="25"/>
       <c r="B85" s="2">
         <v>13</v>
       </c>
@@ -2775,12 +2765,12 @@
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="24"/>
-      <c r="Q85" s="25"/>
+      <c r="O85" s="7"/>
+      <c r="P85" s="21"/>
+      <c r="Q85" s="22"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A86" s="11"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="2">
         <v>14</v>
       </c>
@@ -2796,12 +2786,12 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="24"/>
-      <c r="Q86" s="25"/>
+      <c r="O86" s="7"/>
+      <c r="P86" s="21"/>
+      <c r="Q86" s="22"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B87" s="2">
@@ -2819,12 +2809,12 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
-      <c r="O87" s="10"/>
-      <c r="P87" s="24"/>
-      <c r="Q87" s="25"/>
+      <c r="O87" s="7"/>
+      <c r="P87" s="21"/>
+      <c r="Q87" s="22"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A88" s="11"/>
+      <c r="A88" s="25"/>
       <c r="B88" s="2">
         <v>2</v>
       </c>
@@ -2840,12 +2830,12 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
-      <c r="O88" s="10"/>
-      <c r="P88" s="24"/>
-      <c r="Q88" s="25"/>
+      <c r="O88" s="7"/>
+      <c r="P88" s="21"/>
+      <c r="Q88" s="22"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A89" s="11"/>
+      <c r="A89" s="25"/>
       <c r="B89" s="2">
         <v>3</v>
       </c>
@@ -2861,12 +2851,12 @@
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
-      <c r="O89" s="10"/>
-      <c r="P89" s="24"/>
-      <c r="Q89" s="25"/>
+      <c r="O89" s="7"/>
+      <c r="P89" s="21"/>
+      <c r="Q89" s="22"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A90" s="11"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="2">
         <v>4</v>
       </c>
@@ -2882,12 +2872,12 @@
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
-      <c r="O90" s="10"/>
-      <c r="P90" s="24"/>
-      <c r="Q90" s="25"/>
+      <c r="O90" s="7"/>
+      <c r="P90" s="21"/>
+      <c r="Q90" s="22"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91" s="11"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="2">
         <v>5</v>
       </c>
@@ -2903,12 +2893,12 @@
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
-      <c r="O91" s="10"/>
-      <c r="P91" s="24"/>
-      <c r="Q91" s="25"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="21"/>
+      <c r="Q91" s="22"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" s="11"/>
+      <c r="A92" s="25"/>
       <c r="B92" s="2">
         <v>6</v>
       </c>
@@ -2924,12 +2914,12 @@
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
-      <c r="O92" s="10"/>
-      <c r="P92" s="24"/>
-      <c r="Q92" s="25"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="21"/>
+      <c r="Q92" s="22"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93" s="11"/>
+      <c r="A93" s="25"/>
       <c r="B93" s="2">
         <v>7</v>
       </c>
@@ -2945,12 +2935,12 @@
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
-      <c r="O93" s="10"/>
-      <c r="P93" s="24"/>
-      <c r="Q93" s="25"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="21"/>
+      <c r="Q93" s="22"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A94" s="11"/>
+      <c r="A94" s="25"/>
       <c r="B94" s="2">
         <v>8</v>
       </c>
@@ -2966,12 +2956,12 @@
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
-      <c r="O94" s="10"/>
-      <c r="P94" s="24"/>
-      <c r="Q94" s="25"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="21"/>
+      <c r="Q94" s="22"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A95" s="11"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="2">
         <v>9</v>
       </c>
@@ -2987,12 +2977,12 @@
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
-      <c r="O95" s="10"/>
-      <c r="P95" s="24"/>
-      <c r="Q95" s="25"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="21"/>
+      <c r="Q95" s="22"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A96" s="11"/>
+      <c r="A96" s="25"/>
       <c r="B96" s="2">
         <v>10</v>
       </c>
@@ -3008,12 +2998,12 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
-      <c r="O96" s="10"/>
-      <c r="P96" s="24"/>
-      <c r="Q96" s="25"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="21"/>
+      <c r="Q96" s="22"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A97" s="11"/>
+      <c r="A97" s="25"/>
       <c r="B97" s="2">
         <v>11</v>
       </c>
@@ -3029,12 +3019,12 @@
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
-      <c r="O97" s="10"/>
-      <c r="P97" s="24"/>
-      <c r="Q97" s="25"/>
+      <c r="O97" s="7"/>
+      <c r="P97" s="21"/>
+      <c r="Q97" s="22"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A98" s="11"/>
+      <c r="A98" s="25"/>
       <c r="B98" s="2">
         <v>12</v>
       </c>
@@ -3050,12 +3040,12 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
-      <c r="O98" s="10"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="25"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="21"/>
+      <c r="Q98" s="22"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A99" s="11"/>
+      <c r="A99" s="25"/>
       <c r="B99" s="2">
         <v>13</v>
       </c>
@@ -3071,30 +3061,30 @@
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
-      <c r="O99" s="10"/>
-      <c r="P99" s="24"/>
-      <c r="Q99" s="25"/>
+      <c r="O99" s="7"/>
+      <c r="P99" s="21"/>
+      <c r="Q99" s="22"/>
     </row>
     <row r="100" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
-      <c r="B100" s="13">
+      <c r="A100" s="26"/>
+      <c r="B100" s="10">
         <v>14</v>
       </c>
-      <c r="C100" s="14"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="14"/>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
-      <c r="N100" s="14"/>
-      <c r="O100" s="15"/>
-      <c r="P100" s="26"/>
-      <c r="Q100" s="27"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="11"/>
+      <c r="K100" s="11"/>
+      <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
+      <c r="N100" s="11"/>
+      <c r="O100" s="12"/>
+      <c r="P100" s="23"/>
+      <c r="Q100" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="10">
